--- a/templates/xs_template.xlsx
+++ b/templates/xs_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{320AF6EB-A992-4A7B-99B4-087775789FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1629942E-3C8D-4E50-89C2-ED7033486B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -410,13 +410,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>438150</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:rowOff>44450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>1273175</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>162922</xdr:rowOff>
+      <xdr:rowOff>181972</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -445,8 +445,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="628650" y="139700"/>
-          <a:ext cx="835025" cy="912222"/>
+          <a:off x="638175" y="44450"/>
+          <a:ext cx="835025" cy="899522"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -721,10 +721,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A2:J221"/>
+  <dimension ref="A1:J221"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
@@ -735,21 +732,23 @@
     <col min="11" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C2" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C3" s="13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="14" t="s">
         <v>9</v>
       </c>
     </row>
+    <row r="5" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="6" spans="2:9" s="12" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -2931,7 +2930,7 @@
     <mergeCell ref="B6:I7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/templates/xs_template.xlsx
+++ b/templates/xs_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1629942E-3C8D-4E50-89C2-ED7033486B99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B7BDF8-5C22-4152-B970-4F5D7DE8C231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -333,7 +333,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -342,7 +342,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -366,18 +366,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -408,15 +407,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:colOff>438151</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1273175</xdr:colOff>
+      <xdr:colOff>1266151</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>181972</xdr:rowOff>
+      <xdr:rowOff>167600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -428,7 +427,7 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -445,8 +444,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="638175" y="44450"/>
-          <a:ext cx="835025" cy="899522"/>
+          <a:off x="628651" y="44450"/>
+          <a:ext cx="828000" cy="828000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -721,6 +720,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J221"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
@@ -732,42 +734,42 @@
     <col min="11" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C2" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="5" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="2:9" s="12" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-    </row>
-    <row r="7" spans="2:9" s="12" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
+    <row r="6" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
     </row>
     <row r="8" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
@@ -796,7 +798,7 @@
       </c>
     </row>
     <row r="9" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B9" s="15"/>
+      <c r="B9" s="14"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="3"/>
@@ -806,7 +808,7 @@
       <c r="I9" s="6"/>
     </row>
     <row r="10" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B10" s="16"/>
+      <c r="B10" s="15"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
@@ -816,7 +818,7 @@
       <c r="I10" s="8"/>
     </row>
     <row r="11" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B11" s="16"/>
+      <c r="B11" s="15"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -826,7 +828,7 @@
       <c r="I11" s="8"/>
     </row>
     <row r="12" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B12" s="16"/>
+      <c r="B12" s="15"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -836,7 +838,7 @@
       <c r="I12" s="8"/>
     </row>
     <row r="13" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B13" s="16"/>
+      <c r="B13" s="15"/>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
@@ -846,7 +848,7 @@
       <c r="I13" s="8"/>
     </row>
     <row r="14" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B14" s="16"/>
+      <c r="B14" s="15"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
@@ -856,7 +858,7 @@
       <c r="I14" s="8"/>
     </row>
     <row r="15" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B15" s="16"/>
+      <c r="B15" s="15"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
@@ -866,7 +868,7 @@
       <c r="I15" s="8"/>
     </row>
     <row r="16" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B16" s="16"/>
+      <c r="B16" s="15"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
@@ -876,7 +878,7 @@
       <c r="I16" s="8"/>
     </row>
     <row r="17" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B17" s="16"/>
+      <c r="B17" s="15"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
@@ -886,7 +888,7 @@
       <c r="I17" s="8"/>
     </row>
     <row r="18" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B18" s="16"/>
+      <c r="B18" s="15"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
@@ -896,7 +898,7 @@
       <c r="I18" s="8"/>
     </row>
     <row r="19" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B19" s="16"/>
+      <c r="B19" s="15"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -906,7 +908,7 @@
       <c r="I19" s="8"/>
     </row>
     <row r="20" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B20" s="16"/>
+      <c r="B20" s="15"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
@@ -916,7 +918,7 @@
       <c r="I20" s="8"/>
     </row>
     <row r="21" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B21" s="16"/>
+      <c r="B21" s="15"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
@@ -926,7 +928,7 @@
       <c r="I21" s="8"/>
     </row>
     <row r="22" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B22" s="16"/>
+      <c r="B22" s="15"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -936,7 +938,7 @@
       <c r="I22" s="8"/>
     </row>
     <row r="23" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="16"/>
+      <c r="B23" s="15"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
@@ -946,7 +948,7 @@
       <c r="I23" s="8"/>
     </row>
     <row r="24" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B24" s="16"/>
+      <c r="B24" s="15"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
@@ -956,7 +958,7 @@
       <c r="I24" s="8"/>
     </row>
     <row r="25" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B25" s="16"/>
+      <c r="B25" s="15"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -966,7 +968,7 @@
       <c r="I25" s="8"/>
     </row>
     <row r="26" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B26" s="16"/>
+      <c r="B26" s="15"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
@@ -976,7 +978,7 @@
       <c r="I26" s="8"/>
     </row>
     <row r="27" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B27" s="16"/>
+      <c r="B27" s="15"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
@@ -986,7 +988,7 @@
       <c r="I27" s="8"/>
     </row>
     <row r="28" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B28" s="16"/>
+      <c r="B28" s="15"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
@@ -996,7 +998,7 @@
       <c r="I28" s="8"/>
     </row>
     <row r="29" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B29" s="16"/>
+      <c r="B29" s="15"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
@@ -1006,7 +1008,7 @@
       <c r="I29" s="8"/>
     </row>
     <row r="30" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B30" s="16"/>
+      <c r="B30" s="15"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
@@ -1016,7 +1018,7 @@
       <c r="I30" s="8"/>
     </row>
     <row r="31" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B31" s="16"/>
+      <c r="B31" s="15"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
@@ -1026,7 +1028,7 @@
       <c r="I31" s="8"/>
     </row>
     <row r="32" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B32" s="16"/>
+      <c r="B32" s="15"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
@@ -1036,7 +1038,7 @@
       <c r="I32" s="8"/>
     </row>
     <row r="33" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B33" s="16"/>
+      <c r="B33" s="15"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
@@ -1046,7 +1048,7 @@
       <c r="I33" s="8"/>
     </row>
     <row r="34" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B34" s="16"/>
+      <c r="B34" s="15"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
@@ -1056,7 +1058,7 @@
       <c r="I34" s="8"/>
     </row>
     <row r="35" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B35" s="16"/>
+      <c r="B35" s="15"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -1066,7 +1068,7 @@
       <c r="I35" s="8"/>
     </row>
     <row r="36" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B36" s="16"/>
+      <c r="B36" s="15"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -1076,7 +1078,7 @@
       <c r="I36" s="8"/>
     </row>
     <row r="37" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B37" s="16"/>
+      <c r="B37" s="15"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -1086,7 +1088,7 @@
       <c r="I37" s="8"/>
     </row>
     <row r="38" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B38" s="16"/>
+      <c r="B38" s="15"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
@@ -1096,7 +1098,7 @@
       <c r="I38" s="8"/>
     </row>
     <row r="39" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B39" s="16"/>
+      <c r="B39" s="15"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
@@ -1106,7 +1108,7 @@
       <c r="I39" s="8"/>
     </row>
     <row r="40" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B40" s="16"/>
+      <c r="B40" s="15"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
@@ -1116,7 +1118,7 @@
       <c r="I40" s="8"/>
     </row>
     <row r="41" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B41" s="16"/>
+      <c r="B41" s="15"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
@@ -1126,7 +1128,7 @@
       <c r="I41" s="8"/>
     </row>
     <row r="42" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B42" s="16"/>
+      <c r="B42" s="15"/>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
@@ -1136,7 +1138,7 @@
       <c r="I42" s="8"/>
     </row>
     <row r="43" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B43" s="16"/>
+      <c r="B43" s="15"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
@@ -1146,7 +1148,7 @@
       <c r="I43" s="8"/>
     </row>
     <row r="44" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B44" s="16"/>
+      <c r="B44" s="15"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
@@ -1156,7 +1158,7 @@
       <c r="I44" s="8"/>
     </row>
     <row r="45" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B45" s="16"/>
+      <c r="B45" s="15"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
@@ -1166,7 +1168,7 @@
       <c r="I45" s="8"/>
     </row>
     <row r="46" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B46" s="16"/>
+      <c r="B46" s="15"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
@@ -1176,7 +1178,7 @@
       <c r="I46" s="8"/>
     </row>
     <row r="47" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B47" s="16"/>
+      <c r="B47" s="15"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
@@ -1186,7 +1188,7 @@
       <c r="I47" s="8"/>
     </row>
     <row r="48" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B48" s="17"/>
+      <c r="B48" s="16"/>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>
@@ -2930,7 +2932,7 @@
     <mergeCell ref="B6:I7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/templates/xs_template.xlsx
+++ b/templates/xs_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6B7BDF8-5C22-4152-B970-4F5D7DE8C231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B23A4A-56D4-4C17-9040-7F717772AC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Subsídio de Turno</t>
   </si>
@@ -71,6 +71,9 @@
       </rPr>
       <t>"Cruz Lusa"</t>
     </r>
+  </si>
+  <si>
+    <t>MAPA SALARIAL - ABRIL 2026</t>
   </si>
 </sst>
 </file>
@@ -333,7 +336,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -342,7 +345,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -366,17 +369,18 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -407,15 +411,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>438151</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:colOff>438150</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1266151</xdr:colOff>
+      <xdr:colOff>1273175</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>167600</xdr:rowOff>
+      <xdr:rowOff>162922</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -427,7 +431,7 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvPicPr>
-          <a:picLocks/>
+          <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -444,8 +448,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="628651" y="44450"/>
-          <a:ext cx="828000" cy="828000"/>
+          <a:off x="628650" y="139700"/>
+          <a:ext cx="835025" cy="912222"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -723,7 +727,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J221"/>
+  <dimension ref="A2:J221"/>
   <sheetFormatPr defaultColWidth="0" defaultRowHeight="17.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
@@ -734,42 +738,42 @@
     <col min="11" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:9" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C2" s="11" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="12" t="s">
+    <row r="3" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="13" t="s">
+    <row r="4" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="14" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="6" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-    </row>
-    <row r="7" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
+    <row r="6" spans="2:9" s="12" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+    </row>
+    <row r="7" spans="2:9" s="12" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
     </row>
     <row r="8" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
@@ -798,7 +802,7 @@
       </c>
     </row>
     <row r="9" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B9" s="14"/>
+      <c r="B9" s="15"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
       <c r="E9" s="3"/>
@@ -808,7 +812,7 @@
       <c r="I9" s="6"/>
     </row>
     <row r="10" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B10" s="15"/>
+      <c r="B10" s="16"/>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
@@ -818,7 +822,7 @@
       <c r="I10" s="8"/>
     </row>
     <row r="11" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B11" s="15"/>
+      <c r="B11" s="16"/>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -828,7 +832,7 @@
       <c r="I11" s="8"/>
     </row>
     <row r="12" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B12" s="15"/>
+      <c r="B12" s="16"/>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
@@ -838,7 +842,7 @@
       <c r="I12" s="8"/>
     </row>
     <row r="13" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B13" s="15"/>
+      <c r="B13" s="16"/>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
@@ -848,7 +852,7 @@
       <c r="I13" s="8"/>
     </row>
     <row r="14" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B14" s="15"/>
+      <c r="B14" s="16"/>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
@@ -858,7 +862,7 @@
       <c r="I14" s="8"/>
     </row>
     <row r="15" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B15" s="15"/>
+      <c r="B15" s="16"/>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
@@ -868,7 +872,7 @@
       <c r="I15" s="8"/>
     </row>
     <row r="16" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B16" s="15"/>
+      <c r="B16" s="16"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
@@ -878,7 +882,7 @@
       <c r="I16" s="8"/>
     </row>
     <row r="17" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B17" s="15"/>
+      <c r="B17" s="16"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
@@ -888,7 +892,7 @@
       <c r="I17" s="8"/>
     </row>
     <row r="18" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B18" s="15"/>
+      <c r="B18" s="16"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
@@ -898,7 +902,7 @@
       <c r="I18" s="8"/>
     </row>
     <row r="19" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B19" s="15"/>
+      <c r="B19" s="16"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
@@ -908,7 +912,7 @@
       <c r="I19" s="8"/>
     </row>
     <row r="20" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B20" s="15"/>
+      <c r="B20" s="16"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
@@ -918,7 +922,7 @@
       <c r="I20" s="8"/>
     </row>
     <row r="21" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B21" s="15"/>
+      <c r="B21" s="16"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
@@ -928,7 +932,7 @@
       <c r="I21" s="8"/>
     </row>
     <row r="22" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B22" s="15"/>
+      <c r="B22" s="16"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
@@ -938,7 +942,7 @@
       <c r="I22" s="8"/>
     </row>
     <row r="23" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="15"/>
+      <c r="B23" s="16"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
@@ -948,7 +952,7 @@
       <c r="I23" s="8"/>
     </row>
     <row r="24" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B24" s="15"/>
+      <c r="B24" s="16"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
@@ -958,7 +962,7 @@
       <c r="I24" s="8"/>
     </row>
     <row r="25" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B25" s="15"/>
+      <c r="B25" s="16"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
@@ -968,7 +972,7 @@
       <c r="I25" s="8"/>
     </row>
     <row r="26" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B26" s="15"/>
+      <c r="B26" s="16"/>
       <c r="C26" s="7"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
@@ -978,7 +982,7 @@
       <c r="I26" s="8"/>
     </row>
     <row r="27" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B27" s="15"/>
+      <c r="B27" s="16"/>
       <c r="C27" s="7"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
@@ -988,7 +992,7 @@
       <c r="I27" s="8"/>
     </row>
     <row r="28" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B28" s="15"/>
+      <c r="B28" s="16"/>
       <c r="C28" s="7"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
@@ -998,7 +1002,7 @@
       <c r="I28" s="8"/>
     </row>
     <row r="29" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B29" s="15"/>
+      <c r="B29" s="16"/>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
@@ -1008,7 +1012,7 @@
       <c r="I29" s="8"/>
     </row>
     <row r="30" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B30" s="15"/>
+      <c r="B30" s="16"/>
       <c r="C30" s="7"/>
       <c r="D30" s="7"/>
       <c r="E30" s="7"/>
@@ -1018,7 +1022,7 @@
       <c r="I30" s="8"/>
     </row>
     <row r="31" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B31" s="15"/>
+      <c r="B31" s="16"/>
       <c r="C31" s="7"/>
       <c r="D31" s="7"/>
       <c r="E31" s="7"/>
@@ -1028,7 +1032,7 @@
       <c r="I31" s="8"/>
     </row>
     <row r="32" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B32" s="15"/>
+      <c r="B32" s="16"/>
       <c r="C32" s="7"/>
       <c r="D32" s="7"/>
       <c r="E32" s="7"/>
@@ -1038,7 +1042,7 @@
       <c r="I32" s="8"/>
     </row>
     <row r="33" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B33" s="15"/>
+      <c r="B33" s="16"/>
       <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="7"/>
@@ -1048,7 +1052,7 @@
       <c r="I33" s="8"/>
     </row>
     <row r="34" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B34" s="15"/>
+      <c r="B34" s="16"/>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
       <c r="E34" s="7"/>
@@ -1058,7 +1062,7 @@
       <c r="I34" s="8"/>
     </row>
     <row r="35" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B35" s="15"/>
+      <c r="B35" s="16"/>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -1068,7 +1072,7 @@
       <c r="I35" s="8"/>
     </row>
     <row r="36" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B36" s="15"/>
+      <c r="B36" s="16"/>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -1078,7 +1082,7 @@
       <c r="I36" s="8"/>
     </row>
     <row r="37" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B37" s="15"/>
+      <c r="B37" s="16"/>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -1088,7 +1092,7 @@
       <c r="I37" s="8"/>
     </row>
     <row r="38" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B38" s="15"/>
+      <c r="B38" s="16"/>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
@@ -1098,7 +1102,7 @@
       <c r="I38" s="8"/>
     </row>
     <row r="39" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B39" s="15"/>
+      <c r="B39" s="16"/>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
@@ -1108,7 +1112,7 @@
       <c r="I39" s="8"/>
     </row>
     <row r="40" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B40" s="15"/>
+      <c r="B40" s="16"/>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
@@ -1118,7 +1122,7 @@
       <c r="I40" s="8"/>
     </row>
     <row r="41" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B41" s="15"/>
+      <c r="B41" s="16"/>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
@@ -1128,7 +1132,7 @@
       <c r="I41" s="8"/>
     </row>
     <row r="42" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B42" s="15"/>
+      <c r="B42" s="16"/>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
@@ -1138,7 +1142,7 @@
       <c r="I42" s="8"/>
     </row>
     <row r="43" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B43" s="15"/>
+      <c r="B43" s="16"/>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
@@ -1148,7 +1152,7 @@
       <c r="I43" s="8"/>
     </row>
     <row r="44" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B44" s="15"/>
+      <c r="B44" s="16"/>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
@@ -1158,7 +1162,7 @@
       <c r="I44" s="8"/>
     </row>
     <row r="45" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B45" s="15"/>
+      <c r="B45" s="16"/>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
@@ -1168,7 +1172,7 @@
       <c r="I45" s="8"/>
     </row>
     <row r="46" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B46" s="15"/>
+      <c r="B46" s="16"/>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
@@ -1178,7 +1182,7 @@
       <c r="I46" s="8"/>
     </row>
     <row r="47" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B47" s="15"/>
+      <c r="B47" s="16"/>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
@@ -1188,7 +1192,7 @@
       <c r="I47" s="8"/>
     </row>
     <row r="48" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B48" s="16"/>
+      <c r="B48" s="17"/>
       <c r="C48" s="9"/>
       <c r="D48" s="9"/>
       <c r="E48" s="9"/>

--- a/templates/xs_template.xlsx
+++ b/templates/xs_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7B23A4A-56D4-4C17-9040-7F717772AC02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1B7F0D-A68E-48F3-923C-94FB5B201589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Subsídio de Turno</t>
   </si>
@@ -71,9 +71,6 @@
       </rPr>
       <t>"Cruz Lusa"</t>
     </r>
-  </si>
-  <si>
-    <t>MAPA SALARIAL - ABRIL 2026</t>
   </si>
 </sst>
 </file>
@@ -336,51 +333,32 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -388,6 +366,24 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -412,8 +408,8 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>438150</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>139700</xdr:rowOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>311150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -448,8 +444,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="628650" y="139700"/>
-          <a:ext cx="835025" cy="912222"/>
+          <a:off x="628650" y="533400"/>
+          <a:ext cx="835025" cy="918572"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -739,467 +735,465 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="6" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="7" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="2:9" s="12" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-    </row>
-    <row r="7" spans="2:9" s="12" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
+    <row r="6" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="11"/>
+      <c r="I6" s="11"/>
+    </row>
+    <row r="7" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="12"/>
+      <c r="G7" s="12"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
     </row>
     <row r="8" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B9" s="15"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="6"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="14"/>
     </row>
     <row r="10" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B10" s="16"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="8"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15"/>
+      <c r="G10" s="15"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="16"/>
     </row>
     <row r="11" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B11" s="16"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="8"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15"/>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="16"/>
     </row>
     <row r="12" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B12" s="16"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="15"/>
+      <c r="F12" s="15"/>
+      <c r="G12" s="15"/>
+      <c r="H12" s="15"/>
+      <c r="I12" s="16"/>
     </row>
     <row r="13" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B13" s="16"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="8"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="16"/>
     </row>
     <row r="14" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B14" s="16"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="8"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="16"/>
     </row>
     <row r="15" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B15" s="16"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="8"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="16"/>
     </row>
     <row r="16" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B16" s="16"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="8"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="16"/>
     </row>
     <row r="17" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B17" s="16"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="8"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="16"/>
     </row>
     <row r="18" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B18" s="16"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="8"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="16"/>
     </row>
     <row r="19" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B19" s="16"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="8"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="16"/>
     </row>
     <row r="20" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B20" s="16"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="8"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="16"/>
     </row>
     <row r="21" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B21" s="16"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="8"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="16"/>
     </row>
     <row r="22" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B22" s="16"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="8"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="16"/>
     </row>
     <row r="23" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="16"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="8"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="16"/>
     </row>
     <row r="24" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B24" s="16"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="8"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="16"/>
     </row>
     <row r="25" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B25" s="16"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="8"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="16"/>
     </row>
     <row r="26" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B26" s="16"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="8"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="16"/>
     </row>
     <row r="27" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B27" s="16"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="8"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="16"/>
     </row>
     <row r="28" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B28" s="16"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="8"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="16"/>
     </row>
     <row r="29" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B29" s="16"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="8"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="16"/>
     </row>
     <row r="30" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B30" s="16"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="8"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="16"/>
     </row>
     <row r="31" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B31" s="16"/>
-      <c r="C31" s="7"/>
-      <c r="D31" s="7"/>
-      <c r="E31" s="7"/>
-      <c r="F31" s="7"/>
-      <c r="G31" s="7"/>
-      <c r="H31" s="7"/>
-      <c r="I31" s="8"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="16"/>
     </row>
     <row r="32" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B32" s="16"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-      <c r="H32" s="7"/>
-      <c r="I32" s="8"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="16"/>
     </row>
     <row r="33" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B33" s="16"/>
-      <c r="C33" s="7"/>
-      <c r="D33" s="7"/>
-      <c r="E33" s="7"/>
-      <c r="F33" s="7"/>
-      <c r="G33" s="7"/>
-      <c r="H33" s="7"/>
-      <c r="I33" s="8"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="16"/>
     </row>
     <row r="34" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B34" s="16"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-      <c r="H34" s="7"/>
-      <c r="I34" s="8"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="16"/>
     </row>
     <row r="35" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B35" s="16"/>
-      <c r="C35" s="7"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="7"/>
-      <c r="F35" s="7"/>
-      <c r="G35" s="7"/>
-      <c r="H35" s="7"/>
-      <c r="I35" s="8"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="16"/>
     </row>
     <row r="36" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B36" s="16"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7"/>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-      <c r="H36" s="7"/>
-      <c r="I36" s="8"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="16"/>
     </row>
     <row r="37" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B37" s="16"/>
-      <c r="C37" s="7"/>
-      <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="7"/>
-      <c r="G37" s="7"/>
-      <c r="H37" s="7"/>
-      <c r="I37" s="8"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+      <c r="E37" s="15"/>
+      <c r="F37" s="15"/>
+      <c r="G37" s="15"/>
+      <c r="H37" s="15"/>
+      <c r="I37" s="16"/>
     </row>
     <row r="38" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B38" s="16"/>
-      <c r="C38" s="7"/>
-      <c r="D38" s="7"/>
-      <c r="E38" s="7"/>
-      <c r="F38" s="7"/>
-      <c r="G38" s="7"/>
-      <c r="H38" s="7"/>
-      <c r="I38" s="8"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="15"/>
+      <c r="D38" s="15"/>
+      <c r="E38" s="15"/>
+      <c r="F38" s="15"/>
+      <c r="G38" s="15"/>
+      <c r="H38" s="15"/>
+      <c r="I38" s="16"/>
     </row>
     <row r="39" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B39" s="16"/>
-      <c r="C39" s="7"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
-      <c r="F39" s="7"/>
-      <c r="G39" s="7"/>
-      <c r="H39" s="7"/>
-      <c r="I39" s="8"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="15"/>
+      <c r="D39" s="15"/>
+      <c r="E39" s="15"/>
+      <c r="F39" s="15"/>
+      <c r="G39" s="15"/>
+      <c r="H39" s="15"/>
+      <c r="I39" s="16"/>
     </row>
     <row r="40" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B40" s="16"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
-      <c r="H40" s="7"/>
-      <c r="I40" s="8"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="15"/>
+      <c r="D40" s="15"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="15"/>
+      <c r="G40" s="15"/>
+      <c r="H40" s="15"/>
+      <c r="I40" s="16"/>
     </row>
     <row r="41" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B41" s="16"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="7"/>
-      <c r="G41" s="7"/>
-      <c r="H41" s="7"/>
-      <c r="I41" s="8"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="15"/>
+      <c r="D41" s="15"/>
+      <c r="E41" s="15"/>
+      <c r="F41" s="15"/>
+      <c r="G41" s="15"/>
+      <c r="H41" s="15"/>
+      <c r="I41" s="16"/>
     </row>
     <row r="42" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B42" s="16"/>
-      <c r="C42" s="7"/>
-      <c r="D42" s="7"/>
-      <c r="E42" s="7"/>
-      <c r="F42" s="7"/>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="8"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="15"/>
+      <c r="D42" s="15"/>
+      <c r="E42" s="15"/>
+      <c r="F42" s="15"/>
+      <c r="G42" s="15"/>
+      <c r="H42" s="15"/>
+      <c r="I42" s="16"/>
     </row>
     <row r="43" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B43" s="16"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-      <c r="E43" s="7"/>
-      <c r="F43" s="7"/>
-      <c r="G43" s="7"/>
-      <c r="H43" s="7"/>
-      <c r="I43" s="8"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="15"/>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="16"/>
     </row>
     <row r="44" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B44" s="16"/>
-      <c r="C44" s="7"/>
-      <c r="D44" s="7"/>
-      <c r="E44" s="7"/>
-      <c r="F44" s="7"/>
-      <c r="G44" s="7"/>
-      <c r="H44" s="7"/>
-      <c r="I44" s="8"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="15"/>
+      <c r="D44" s="15"/>
+      <c r="E44" s="15"/>
+      <c r="F44" s="15"/>
+      <c r="G44" s="15"/>
+      <c r="H44" s="15"/>
+      <c r="I44" s="16"/>
     </row>
     <row r="45" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B45" s="16"/>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="8"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="15"/>
+      <c r="D45" s="15"/>
+      <c r="E45" s="15"/>
+      <c r="F45" s="15"/>
+      <c r="G45" s="15"/>
+      <c r="H45" s="15"/>
+      <c r="I45" s="16"/>
     </row>
     <row r="46" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B46" s="16"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="8"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="15"/>
+      <c r="D46" s="15"/>
+      <c r="E46" s="15"/>
+      <c r="F46" s="15"/>
+      <c r="G46" s="15"/>
+      <c r="H46" s="15"/>
+      <c r="I46" s="16"/>
     </row>
     <row r="47" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B47" s="16"/>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="8"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
+      <c r="E47" s="15"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="15"/>
+      <c r="H47" s="15"/>
+      <c r="I47" s="16"/>
     </row>
     <row r="48" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B48" s="17"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="9"/>
-      <c r="E48" s="9"/>
-      <c r="F48" s="9"/>
-      <c r="G48" s="9"/>
-      <c r="H48" s="9"/>
-      <c r="I48" s="10"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+      <c r="H48" s="17"/>
+      <c r="I48" s="18"/>
     </row>
     <row r="49" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="2"/>

--- a/templates/xs_template.xlsx
+++ b/templates/xs_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC1B7F0D-A68E-48F3-923C-94FB5B201589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36153880-F8FA-479E-8972-4A56E94D0260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -333,14 +333,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -367,22 +364,22 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -728,472 +725,472 @@
   <cols>
     <col min="1" max="1" width="2.85546875" customWidth="1"/>
     <col min="2" max="2" width="24.140625" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" style="1" customWidth="1"/>
-    <col min="5" max="9" width="15.7109375" customWidth="1"/>
+    <col min="3" max="4" width="21.42578125" style="1" customWidth="1"/>
+    <col min="5" max="9" width="21.42578125" customWidth="1"/>
     <col min="10" max="10" width="2.85546875" customWidth="1"/>
     <col min="11" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="11"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-      <c r="I6" s="11"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
     </row>
     <row r="7" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
-      <c r="H7" s="12"/>
-      <c r="I7" s="12"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
     </row>
     <row r="8" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B9" s="8"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="14"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="13"/>
     </row>
     <row r="10" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B10" s="9"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="15"/>
-      <c r="E10" s="15"/>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="15"/>
-      <c r="I10" s="16"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="15"/>
     </row>
     <row r="11" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B11" s="9"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="16"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="15"/>
     </row>
     <row r="12" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B12" s="9"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="16"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="15"/>
     </row>
     <row r="13" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B13" s="9"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
-      <c r="G13" s="15"/>
-      <c r="H13" s="15"/>
-      <c r="I13" s="16"/>
+      <c r="B13" s="8"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="15"/>
     </row>
     <row r="14" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B14" s="9"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
-      <c r="G14" s="15"/>
-      <c r="H14" s="15"/>
-      <c r="I14" s="16"/>
+      <c r="B14" s="8"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="15"/>
     </row>
     <row r="15" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B15" s="9"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="16"/>
+      <c r="B15" s="8"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="15"/>
     </row>
     <row r="16" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B16" s="9"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="16"/>
+      <c r="B16" s="8"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="15"/>
     </row>
     <row r="17" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B17" s="9"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="16"/>
+      <c r="B17" s="8"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="15"/>
     </row>
     <row r="18" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B18" s="9"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="16"/>
+      <c r="B18" s="8"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="15"/>
     </row>
     <row r="19" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B19" s="9"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="16"/>
+      <c r="B19" s="8"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="15"/>
     </row>
     <row r="20" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B20" s="9"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="16"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="15"/>
     </row>
     <row r="21" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B21" s="9"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="16"/>
+      <c r="B21" s="8"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="15"/>
     </row>
     <row r="22" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B22" s="9"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="16"/>
+      <c r="B22" s="8"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="15"/>
     </row>
     <row r="23" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B23" s="9"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="16"/>
+      <c r="B23" s="8"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="15"/>
     </row>
     <row r="24" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B24" s="9"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="15"/>
-      <c r="E24" s="15"/>
-      <c r="F24" s="15"/>
-      <c r="G24" s="15"/>
-      <c r="H24" s="15"/>
-      <c r="I24" s="16"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="15"/>
     </row>
     <row r="25" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B25" s="9"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="16"/>
+      <c r="B25" s="8"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="15"/>
     </row>
     <row r="26" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B26" s="9"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="15"/>
-      <c r="E26" s="15"/>
-      <c r="F26" s="15"/>
-      <c r="G26" s="15"/>
-      <c r="H26" s="15"/>
-      <c r="I26" s="16"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="15"/>
     </row>
     <row r="27" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B27" s="9"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
-      <c r="I27" s="16"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="15"/>
     </row>
     <row r="28" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B28" s="9"/>
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="15"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="15"/>
-      <c r="I28" s="16"/>
+      <c r="B28" s="8"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="15"/>
     </row>
     <row r="29" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B29" s="9"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="15"/>
-      <c r="E29" s="15"/>
-      <c r="F29" s="15"/>
-      <c r="G29" s="15"/>
-      <c r="H29" s="15"/>
-      <c r="I29" s="16"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="15"/>
     </row>
     <row r="30" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B30" s="9"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="15"/>
-      <c r="E30" s="15"/>
-      <c r="F30" s="15"/>
-      <c r="G30" s="15"/>
-      <c r="H30" s="15"/>
-      <c r="I30" s="16"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="15"/>
     </row>
     <row r="31" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B31" s="9"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="15"/>
-      <c r="E31" s="15"/>
-      <c r="F31" s="15"/>
-      <c r="G31" s="15"/>
-      <c r="H31" s="15"/>
-      <c r="I31" s="16"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="15"/>
     </row>
     <row r="32" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B32" s="9"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="15"/>
-      <c r="E32" s="15"/>
-      <c r="F32" s="15"/>
-      <c r="G32" s="15"/>
-      <c r="H32" s="15"/>
-      <c r="I32" s="16"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="15"/>
     </row>
     <row r="33" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B33" s="9"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="15"/>
-      <c r="E33" s="15"/>
-      <c r="F33" s="15"/>
-      <c r="G33" s="15"/>
-      <c r="H33" s="15"/>
-      <c r="I33" s="16"/>
+      <c r="B33" s="8"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="15"/>
     </row>
     <row r="34" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B34" s="9"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="15"/>
-      <c r="E34" s="15"/>
-      <c r="F34" s="15"/>
-      <c r="G34" s="15"/>
-      <c r="H34" s="15"/>
-      <c r="I34" s="16"/>
+      <c r="B34" s="8"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="15"/>
     </row>
     <row r="35" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B35" s="9"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="16"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="15"/>
     </row>
     <row r="36" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B36" s="9"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="15"/>
-      <c r="E36" s="15"/>
-      <c r="F36" s="15"/>
-      <c r="G36" s="15"/>
-      <c r="H36" s="15"/>
-      <c r="I36" s="16"/>
+      <c r="B36" s="8"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="15"/>
     </row>
     <row r="37" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B37" s="9"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="15"/>
-      <c r="E37" s="15"/>
-      <c r="F37" s="15"/>
-      <c r="G37" s="15"/>
-      <c r="H37" s="15"/>
-      <c r="I37" s="16"/>
+      <c r="B37" s="8"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="15"/>
     </row>
     <row r="38" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B38" s="9"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="15"/>
-      <c r="E38" s="15"/>
-      <c r="F38" s="15"/>
-      <c r="G38" s="15"/>
-      <c r="H38" s="15"/>
-      <c r="I38" s="16"/>
+      <c r="B38" s="8"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="15"/>
     </row>
     <row r="39" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B39" s="9"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="15"/>
-      <c r="E39" s="15"/>
-      <c r="F39" s="15"/>
-      <c r="G39" s="15"/>
-      <c r="H39" s="15"/>
-      <c r="I39" s="16"/>
+      <c r="B39" s="8"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="15"/>
     </row>
     <row r="40" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B40" s="9"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="15"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="15"/>
-      <c r="G40" s="15"/>
-      <c r="H40" s="15"/>
-      <c r="I40" s="16"/>
+      <c r="B40" s="8"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="15"/>
     </row>
     <row r="41" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B41" s="9"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15"/>
-      <c r="F41" s="15"/>
-      <c r="G41" s="15"/>
-      <c r="H41" s="15"/>
-      <c r="I41" s="16"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="15"/>
     </row>
     <row r="42" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B42" s="9"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="15"/>
-      <c r="E42" s="15"/>
-      <c r="F42" s="15"/>
-      <c r="G42" s="15"/>
-      <c r="H42" s="15"/>
-      <c r="I42" s="16"/>
+      <c r="B42" s="8"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="15"/>
     </row>
     <row r="43" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B43" s="9"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="15"/>
-      <c r="E43" s="15"/>
-      <c r="F43" s="15"/>
-      <c r="G43" s="15"/>
-      <c r="H43" s="15"/>
-      <c r="I43" s="16"/>
+      <c r="B43" s="8"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="15"/>
     </row>
     <row r="44" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B44" s="9"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="15"/>
-      <c r="E44" s="15"/>
-      <c r="F44" s="15"/>
-      <c r="G44" s="15"/>
-      <c r="H44" s="15"/>
-      <c r="I44" s="16"/>
+      <c r="B44" s="8"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="15"/>
     </row>
     <row r="45" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B45" s="9"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="15"/>
-      <c r="E45" s="15"/>
-      <c r="F45" s="15"/>
-      <c r="G45" s="15"/>
-      <c r="H45" s="15"/>
-      <c r="I45" s="16"/>
+      <c r="B45" s="8"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="15"/>
     </row>
     <row r="46" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B46" s="9"/>
-      <c r="C46" s="15"/>
-      <c r="D46" s="15"/>
-      <c r="E46" s="15"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="15"/>
-      <c r="H46" s="15"/>
-      <c r="I46" s="16"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="15"/>
     </row>
     <row r="47" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B47" s="9"/>
-      <c r="C47" s="15"/>
-      <c r="D47" s="15"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
-      <c r="G47" s="15"/>
-      <c r="H47" s="15"/>
-      <c r="I47" s="16"/>
+      <c r="B47" s="8"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="15"/>
     </row>
     <row r="48" spans="2:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="B48" s="10"/>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
-      <c r="G48" s="17"/>
-      <c r="H48" s="17"/>
-      <c r="I48" s="18"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="17"/>
     </row>
     <row r="49" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="2"/>

--- a/templates/xs_template.xlsx
+++ b/templates/xs_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36153880-F8FA-479E-8972-4A56E94D0260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF308746-E0DE-464D-9B43-7073F021B23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -358,29 +358,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -747,24 +747,24 @@
       </c>
     </row>
     <row r="6" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
     </row>
     <row r="7" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
     </row>
     <row r="8" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
@@ -792,407 +792,407 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="7"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="13"/>
-    </row>
-    <row r="10" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="8"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15"/>
-    </row>
-    <row r="11" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="13"/>
+    </row>
+    <row r="11" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="8"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15"/>
-    </row>
-    <row r="12" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="13"/>
+    </row>
+    <row r="12" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="8"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15"/>
-    </row>
-    <row r="13" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="13"/>
+    </row>
+    <row r="13" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="8"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15"/>
-    </row>
-    <row r="14" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="13"/>
+    </row>
+    <row r="14" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="8"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15"/>
-    </row>
-    <row r="15" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="13"/>
+    </row>
+    <row r="15" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="8"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15"/>
-    </row>
-    <row r="16" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="13"/>
+    </row>
+    <row r="16" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="8"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15"/>
-    </row>
-    <row r="17" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="13"/>
+    </row>
+    <row r="17" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="8"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15"/>
-    </row>
-    <row r="18" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="13"/>
+    </row>
+    <row r="18" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="8"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15"/>
-    </row>
-    <row r="19" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="13"/>
+    </row>
+    <row r="19" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="8"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15"/>
-    </row>
-    <row r="20" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="13"/>
+    </row>
+    <row r="20" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="8"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15"/>
-    </row>
-    <row r="21" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="13"/>
+    </row>
+    <row r="21" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="8"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15"/>
-    </row>
-    <row r="22" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="13"/>
+    </row>
+    <row r="22" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="8"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15"/>
-    </row>
-    <row r="23" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="13"/>
+    </row>
+    <row r="23" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="8"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15"/>
-    </row>
-    <row r="24" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="13"/>
+    </row>
+    <row r="24" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="8"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15"/>
-    </row>
-    <row r="25" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="13"/>
+    </row>
+    <row r="25" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="8"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15"/>
-    </row>
-    <row r="26" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="13"/>
+    </row>
+    <row r="26" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="8"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15"/>
-    </row>
-    <row r="27" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="13"/>
+    </row>
+    <row r="27" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="8"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15"/>
-    </row>
-    <row r="28" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="13"/>
+    </row>
+    <row r="28" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="8"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15"/>
-    </row>
-    <row r="29" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="13"/>
+    </row>
+    <row r="29" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="8"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15"/>
-    </row>
-    <row r="30" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="13"/>
+    </row>
+    <row r="30" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="8"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15"/>
-    </row>
-    <row r="31" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="13"/>
+    </row>
+    <row r="31" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="8"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15"/>
-    </row>
-    <row r="32" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="13"/>
+    </row>
+    <row r="32" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="8"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15"/>
-    </row>
-    <row r="33" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="13"/>
+    </row>
+    <row r="33" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="8"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15"/>
-    </row>
-    <row r="34" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="13"/>
+    </row>
+    <row r="34" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="8"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15"/>
-    </row>
-    <row r="35" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="13"/>
+    </row>
+    <row r="35" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="8"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15"/>
-    </row>
-    <row r="36" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="13"/>
+    </row>
+    <row r="36" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="8"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15"/>
-    </row>
-    <row r="37" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="13"/>
+    </row>
+    <row r="37" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="8"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15"/>
-    </row>
-    <row r="38" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="13"/>
+    </row>
+    <row r="38" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="8"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15"/>
-    </row>
-    <row r="39" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="13"/>
+    </row>
+    <row r="39" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="8"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15"/>
-    </row>
-    <row r="40" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="13"/>
+    </row>
+    <row r="40" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="8"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15"/>
-    </row>
-    <row r="41" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="13"/>
+    </row>
+    <row r="41" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="8"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15"/>
-    </row>
-    <row r="42" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="13"/>
+    </row>
+    <row r="42" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="8"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15"/>
-    </row>
-    <row r="43" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="13"/>
+    </row>
+    <row r="43" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="8"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15"/>
-    </row>
-    <row r="44" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="13"/>
+    </row>
+    <row r="44" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="8"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15"/>
-    </row>
-    <row r="45" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="13"/>
+    </row>
+    <row r="45" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="8"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15"/>
-    </row>
-    <row r="46" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="13"/>
+    </row>
+    <row r="46" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="8"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15"/>
-    </row>
-    <row r="47" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="13"/>
+    </row>
+    <row r="47" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="8"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15"/>
-    </row>
-    <row r="48" spans="2:9" ht="15" x14ac:dyDescent="0.25">
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="13"/>
+    </row>
+    <row r="48" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="9"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="16"/>
-      <c r="I48" s="17"/>
-    </row>
-    <row r="49" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="15"/>
+    </row>
+    <row r="49" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -1202,7 +1202,7 @@
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
     </row>
-    <row r="50" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -1212,7 +1212,7 @@
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
     </row>
-    <row r="51" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
@@ -1222,7 +1222,7 @@
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
     </row>
-    <row r="52" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -1232,7 +1232,7 @@
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
     </row>
-    <row r="53" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -1242,7 +1242,7 @@
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
     </row>
-    <row r="54" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -1252,7 +1252,7 @@
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
     </row>
-    <row r="55" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -1262,7 +1262,7 @@
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
     </row>
-    <row r="56" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
@@ -1272,7 +1272,7 @@
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
     </row>
-    <row r="57" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -1282,7 +1282,7 @@
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
     </row>
-    <row r="58" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
@@ -1292,7 +1292,7 @@
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
     </row>
-    <row r="59" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -1302,7 +1302,7 @@
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
     </row>
-    <row r="60" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
@@ -1312,7 +1312,7 @@
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
     </row>
-    <row r="61" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
@@ -1322,7 +1322,7 @@
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
     </row>
-    <row r="62" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -1332,7 +1332,7 @@
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
     </row>
-    <row r="63" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -1342,7 +1342,7 @@
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
     </row>
-    <row r="64" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -1352,7 +1352,7 @@
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
     </row>
-    <row r="65" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -1362,7 +1362,7 @@
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
     </row>
-    <row r="66" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
@@ -1372,7 +1372,7 @@
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
     </row>
-    <row r="67" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -1382,7 +1382,7 @@
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
     </row>
-    <row r="68" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
@@ -1392,7 +1392,7 @@
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
     </row>
-    <row r="69" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -1402,7 +1402,7 @@
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
     </row>
-    <row r="70" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
@@ -1412,7 +1412,7 @@
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
     </row>
-    <row r="71" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -1422,7 +1422,7 @@
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
     </row>
-    <row r="72" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
@@ -1432,7 +1432,7 @@
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
     </row>
-    <row r="73" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
@@ -1442,7 +1442,7 @@
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
     </row>
-    <row r="74" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
@@ -1452,7 +1452,7 @@
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
     </row>
-    <row r="75" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
@@ -1462,7 +1462,7 @@
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
     </row>
-    <row r="76" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
@@ -1472,7 +1472,7 @@
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
     </row>
-    <row r="77" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
@@ -1482,7 +1482,7 @@
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
     </row>
-    <row r="78" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
@@ -1492,7 +1492,7 @@
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
     </row>
-    <row r="79" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
@@ -1502,7 +1502,7 @@
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
     </row>
-    <row r="80" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
@@ -1512,7 +1512,7 @@
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
     </row>
-    <row r="81" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
@@ -1522,7 +1522,7 @@
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
     </row>
-    <row r="82" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
@@ -1532,7 +1532,7 @@
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
     </row>
-    <row r="83" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
@@ -1542,7 +1542,7 @@
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
     </row>
-    <row r="84" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
@@ -1552,7 +1552,7 @@
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
     </row>
-    <row r="85" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
@@ -1562,7 +1562,7 @@
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
     </row>
-    <row r="86" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
@@ -1572,7 +1572,7 @@
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
     </row>
-    <row r="87" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
@@ -1582,7 +1582,7 @@
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
     </row>
-    <row r="88" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
@@ -1592,7 +1592,7 @@
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
     </row>
-    <row r="89" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
@@ -1602,7 +1602,7 @@
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
     </row>
-    <row r="90" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
@@ -1612,7 +1612,7 @@
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
     </row>
-    <row r="91" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
@@ -1622,7 +1622,7 @@
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
     </row>
-    <row r="92" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
@@ -1632,7 +1632,7 @@
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
     </row>
-    <row r="93" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
@@ -1642,7 +1642,7 @@
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
     </row>
-    <row r="94" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
@@ -1652,7 +1652,7 @@
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
     </row>
-    <row r="95" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
@@ -1662,7 +1662,7 @@
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
     </row>
-    <row r="96" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
@@ -1672,7 +1672,7 @@
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
     </row>
-    <row r="97" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
@@ -1682,7 +1682,7 @@
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
     </row>
-    <row r="98" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
@@ -1692,7 +1692,7 @@
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
     </row>
-    <row r="99" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
@@ -1702,7 +1702,7 @@
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
     </row>
-    <row r="100" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
@@ -1712,7 +1712,7 @@
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
     </row>
-    <row r="101" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
@@ -1722,7 +1722,7 @@
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
     </row>
-    <row r="102" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
@@ -1732,7 +1732,7 @@
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
     </row>
-    <row r="103" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
@@ -1742,7 +1742,7 @@
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
     </row>
-    <row r="104" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>

--- a/templates/xs_template.xlsx
+++ b/templates/xs_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF308746-E0DE-464D-9B43-7073F021B23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36153880-F8FA-479E-8972-4A56E94D0260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -358,29 +358,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -747,24 +747,24 @@
       </c>
     </row>
     <row r="6" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="16"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
+      <c r="G6" s="10"/>
+      <c r="H6" s="10"/>
+      <c r="I6" s="10"/>
     </row>
     <row r="7" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="11"/>
+      <c r="I7" s="11"/>
     </row>
     <row r="8" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
@@ -792,407 +792,407 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B9" s="7"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="11"/>
-    </row>
-    <row r="10" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="13"/>
+    </row>
+    <row r="10" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B10" s="8"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12"/>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12"/>
-      <c r="H10" s="12"/>
-      <c r="I10" s="13"/>
-    </row>
-    <row r="11" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="15"/>
+    </row>
+    <row r="11" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B11" s="8"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="12"/>
-      <c r="E11" s="12"/>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="13"/>
-    </row>
-    <row r="12" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="15"/>
+    </row>
+    <row r="12" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B12" s="8"/>
-      <c r="C12" s="12"/>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12"/>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12"/>
-      <c r="H12" s="12"/>
-      <c r="I12" s="13"/>
-    </row>
-    <row r="13" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="15"/>
+    </row>
+    <row r="13" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B13" s="8"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="13"/>
-    </row>
-    <row r="14" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="15"/>
+    </row>
+    <row r="14" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B14" s="8"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
-      <c r="I14" s="13"/>
-    </row>
-    <row r="15" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="15"/>
+    </row>
+    <row r="15" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B15" s="8"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="13"/>
-    </row>
-    <row r="16" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="15"/>
+    </row>
+    <row r="16" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B16" s="8"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="13"/>
-    </row>
-    <row r="17" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="14"/>
+      <c r="I16" s="15"/>
+    </row>
+    <row r="17" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B17" s="8"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="13"/>
-    </row>
-    <row r="18" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="15"/>
+    </row>
+    <row r="18" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B18" s="8"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="13"/>
-    </row>
-    <row r="19" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="15"/>
+    </row>
+    <row r="19" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B19" s="8"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="13"/>
-    </row>
-    <row r="20" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="15"/>
+    </row>
+    <row r="20" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B20" s="8"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
-      <c r="H20" s="12"/>
-      <c r="I20" s="13"/>
-    </row>
-    <row r="21" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="15"/>
+    </row>
+    <row r="21" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B21" s="8"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
-      <c r="H21" s="12"/>
-      <c r="I21" s="13"/>
-    </row>
-    <row r="22" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="15"/>
+    </row>
+    <row r="22" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B22" s="8"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
-      <c r="H22" s="12"/>
-      <c r="I22" s="13"/>
-    </row>
-    <row r="23" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="15"/>
+    </row>
+    <row r="23" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B23" s="8"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="13"/>
-    </row>
-    <row r="24" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="15"/>
+    </row>
+    <row r="24" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B24" s="8"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
-      <c r="I24" s="13"/>
-    </row>
-    <row r="25" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="15"/>
+    </row>
+    <row r="25" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B25" s="8"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-      <c r="H25" s="12"/>
-      <c r="I25" s="13"/>
-    </row>
-    <row r="26" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="15"/>
+    </row>
+    <row r="26" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B26" s="8"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="13"/>
-    </row>
-    <row r="27" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="15"/>
+    </row>
+    <row r="27" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B27" s="8"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="13"/>
-    </row>
-    <row r="28" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="15"/>
+    </row>
+    <row r="28" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B28" s="8"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
-      <c r="H28" s="12"/>
-      <c r="I28" s="13"/>
-    </row>
-    <row r="29" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="15"/>
+    </row>
+    <row r="29" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B29" s="8"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
-      <c r="H29" s="12"/>
-      <c r="I29" s="13"/>
-    </row>
-    <row r="30" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="15"/>
+    </row>
+    <row r="30" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B30" s="8"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="12"/>
-      <c r="G30" s="12"/>
-      <c r="H30" s="12"/>
-      <c r="I30" s="13"/>
-    </row>
-    <row r="31" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="15"/>
+    </row>
+    <row r="31" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B31" s="8"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="13"/>
-    </row>
-    <row r="32" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="15"/>
+    </row>
+    <row r="32" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B32" s="8"/>
-      <c r="C32" s="12"/>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12"/>
-      <c r="F32" s="12"/>
-      <c r="G32" s="12"/>
-      <c r="H32" s="12"/>
-      <c r="I32" s="13"/>
-    </row>
-    <row r="33" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="15"/>
+    </row>
+    <row r="33" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B33" s="8"/>
-      <c r="C33" s="12"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
-      <c r="F33" s="12"/>
-      <c r="G33" s="12"/>
-      <c r="H33" s="12"/>
-      <c r="I33" s="13"/>
-    </row>
-    <row r="34" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="15"/>
+    </row>
+    <row r="34" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B34" s="8"/>
-      <c r="C34" s="12"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
-      <c r="F34" s="12"/>
-      <c r="G34" s="12"/>
-      <c r="H34" s="12"/>
-      <c r="I34" s="13"/>
-    </row>
-    <row r="35" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="15"/>
+    </row>
+    <row r="35" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B35" s="8"/>
-      <c r="C35" s="12"/>
-      <c r="D35" s="12"/>
-      <c r="E35" s="12"/>
-      <c r="F35" s="12"/>
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="13"/>
-    </row>
-    <row r="36" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="15"/>
+    </row>
+    <row r="36" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B36" s="8"/>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
-      <c r="E36" s="12"/>
-      <c r="F36" s="12"/>
-      <c r="G36" s="12"/>
-      <c r="H36" s="12"/>
-      <c r="I36" s="13"/>
-    </row>
-    <row r="37" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="15"/>
+    </row>
+    <row r="37" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B37" s="8"/>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
-      <c r="F37" s="12"/>
-      <c r="G37" s="12"/>
-      <c r="H37" s="12"/>
-      <c r="I37" s="13"/>
-    </row>
-    <row r="38" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="15"/>
+    </row>
+    <row r="38" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B38" s="8"/>
-      <c r="C38" s="12"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
-      <c r="F38" s="12"/>
-      <c r="G38" s="12"/>
-      <c r="H38" s="12"/>
-      <c r="I38" s="13"/>
-    </row>
-    <row r="39" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="15"/>
+    </row>
+    <row r="39" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B39" s="8"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="13"/>
-    </row>
-    <row r="40" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+      <c r="G39" s="14"/>
+      <c r="H39" s="14"/>
+      <c r="I39" s="15"/>
+    </row>
+    <row r="40" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B40" s="8"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
-      <c r="H40" s="12"/>
-      <c r="I40" s="13"/>
-    </row>
-    <row r="41" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="15"/>
+    </row>
+    <row r="41" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B41" s="8"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="13"/>
-    </row>
-    <row r="42" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C41" s="14"/>
+      <c r="D41" s="14"/>
+      <c r="E41" s="14"/>
+      <c r="F41" s="14"/>
+      <c r="G41" s="14"/>
+      <c r="H41" s="14"/>
+      <c r="I41" s="15"/>
+    </row>
+    <row r="42" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B42" s="8"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
-      <c r="H42" s="12"/>
-      <c r="I42" s="13"/>
-    </row>
-    <row r="43" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+      <c r="G42" s="14"/>
+      <c r="H42" s="14"/>
+      <c r="I42" s="15"/>
+    </row>
+    <row r="43" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B43" s="8"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="13"/>
-    </row>
-    <row r="44" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="15"/>
+    </row>
+    <row r="44" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B44" s="8"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
-      <c r="H44" s="12"/>
-      <c r="I44" s="13"/>
-    </row>
-    <row r="45" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C44" s="14"/>
+      <c r="D44" s="14"/>
+      <c r="E44" s="14"/>
+      <c r="F44" s="14"/>
+      <c r="G44" s="14"/>
+      <c r="H44" s="14"/>
+      <c r="I44" s="15"/>
+    </row>
+    <row r="45" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B45" s="8"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="13"/>
-    </row>
-    <row r="46" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="15"/>
+    </row>
+    <row r="46" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B46" s="8"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
-      <c r="H46" s="12"/>
-      <c r="I46" s="13"/>
-    </row>
-    <row r="47" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="14"/>
+      <c r="G46" s="14"/>
+      <c r="H46" s="14"/>
+      <c r="I46" s="15"/>
+    </row>
+    <row r="47" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B47" s="8"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
-      <c r="H47" s="12"/>
-      <c r="I47" s="13"/>
-    </row>
-    <row r="48" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="15"/>
+    </row>
+    <row r="48" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B48" s="9"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15"/>
-    </row>
-    <row r="49" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C48" s="16"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="16"/>
+      <c r="G48" s="16"/>
+      <c r="H48" s="16"/>
+      <c r="I48" s="17"/>
+    </row>
+    <row r="49" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="D49" s="2"/>
@@ -1202,7 +1202,7 @@
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
     </row>
-    <row r="50" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
@@ -1212,7 +1212,7 @@
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
     </row>
-    <row r="51" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="D51" s="2"/>
@@ -1222,7 +1222,7 @@
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
     </row>
-    <row r="52" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
@@ -1232,7 +1232,7 @@
       <c r="H52" s="2"/>
       <c r="I52" s="2"/>
     </row>
-    <row r="53" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
@@ -1242,7 +1242,7 @@
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
     </row>
-    <row r="54" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
@@ -1252,7 +1252,7 @@
       <c r="H54" s="2"/>
       <c r="I54" s="2"/>
     </row>
-    <row r="55" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
@@ -1262,7 +1262,7 @@
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
     </row>
-    <row r="56" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="D56" s="2"/>
@@ -1272,7 +1272,7 @@
       <c r="H56" s="2"/>
       <c r="I56" s="2"/>
     </row>
-    <row r="57" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="D57" s="2"/>
@@ -1282,7 +1282,7 @@
       <c r="H57" s="2"/>
       <c r="I57" s="2"/>
     </row>
-    <row r="58" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="D58" s="2"/>
@@ -1292,7 +1292,7 @@
       <c r="H58" s="2"/>
       <c r="I58" s="2"/>
     </row>
-    <row r="59" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
@@ -1302,7 +1302,7 @@
       <c r="H59" s="2"/>
       <c r="I59" s="2"/>
     </row>
-    <row r="60" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
@@ -1312,7 +1312,7 @@
       <c r="H60" s="2"/>
       <c r="I60" s="2"/>
     </row>
-    <row r="61" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
       <c r="D61" s="2"/>
@@ -1322,7 +1322,7 @@
       <c r="H61" s="2"/>
       <c r="I61" s="2"/>
     </row>
-    <row r="62" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
       <c r="D62" s="2"/>
@@ -1332,7 +1332,7 @@
       <c r="H62" s="2"/>
       <c r="I62" s="2"/>
     </row>
-    <row r="63" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
       <c r="D63" s="2"/>
@@ -1342,7 +1342,7 @@
       <c r="H63" s="2"/>
       <c r="I63" s="2"/>
     </row>
-    <row r="64" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
       <c r="D64" s="2"/>
@@ -1352,7 +1352,7 @@
       <c r="H64" s="2"/>
       <c r="I64" s="2"/>
     </row>
-    <row r="65" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
@@ -1362,7 +1362,7 @@
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
     </row>
-    <row r="66" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
@@ -1372,7 +1372,7 @@
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
     </row>
-    <row r="67" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
       <c r="D67" s="2"/>
@@ -1382,7 +1382,7 @@
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
     </row>
-    <row r="68" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
@@ -1392,7 +1392,7 @@
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
     </row>
-    <row r="69" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
@@ -1402,7 +1402,7 @@
       <c r="H69" s="2"/>
       <c r="I69" s="2"/>
     </row>
-    <row r="70" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
@@ -1412,7 +1412,7 @@
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
     </row>
-    <row r="71" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
@@ -1422,7 +1422,7 @@
       <c r="H71" s="2"/>
       <c r="I71" s="2"/>
     </row>
-    <row r="72" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
@@ -1432,7 +1432,7 @@
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
     </row>
-    <row r="73" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
@@ -1442,7 +1442,7 @@
       <c r="H73" s="2"/>
       <c r="I73" s="2"/>
     </row>
-    <row r="74" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
@@ -1452,7 +1452,7 @@
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
     </row>
-    <row r="75" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
@@ -1462,7 +1462,7 @@
       <c r="H75" s="2"/>
       <c r="I75" s="2"/>
     </row>
-    <row r="76" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
       <c r="D76" s="2"/>
@@ -1472,7 +1472,7 @@
       <c r="H76" s="2"/>
       <c r="I76" s="2"/>
     </row>
-    <row r="77" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
       <c r="D77" s="2"/>
@@ -1482,7 +1482,7 @@
       <c r="H77" s="2"/>
       <c r="I77" s="2"/>
     </row>
-    <row r="78" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
       <c r="D78" s="2"/>
@@ -1492,7 +1492,7 @@
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
     </row>
-    <row r="79" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
       <c r="D79" s="2"/>
@@ -1502,7 +1502,7 @@
       <c r="H79" s="2"/>
       <c r="I79" s="2"/>
     </row>
-    <row r="80" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
       <c r="D80" s="2"/>
@@ -1512,7 +1512,7 @@
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
     </row>
-    <row r="81" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
@@ -1522,7 +1522,7 @@
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
     </row>
-    <row r="82" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
@@ -1532,7 +1532,7 @@
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
     </row>
-    <row r="83" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
@@ -1542,7 +1542,7 @@
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
     </row>
-    <row r="84" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
@@ -1552,7 +1552,7 @@
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
     </row>
-    <row r="85" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
@@ -1562,7 +1562,7 @@
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
     </row>
-    <row r="86" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
       <c r="D86" s="2"/>
@@ -1572,7 +1572,7 @@
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
     </row>
-    <row r="87" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
@@ -1582,7 +1582,7 @@
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
     </row>
-    <row r="88" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
@@ -1592,7 +1592,7 @@
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
     </row>
-    <row r="89" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
@@ -1602,7 +1602,7 @@
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
     </row>
-    <row r="90" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
@@ -1612,7 +1612,7 @@
       <c r="H90" s="2"/>
       <c r="I90" s="2"/>
     </row>
-    <row r="91" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
@@ -1622,7 +1622,7 @@
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
     </row>
-    <row r="92" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
@@ -1632,7 +1632,7 @@
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
     </row>
-    <row r="93" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
@@ -1642,7 +1642,7 @@
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
     </row>
-    <row r="94" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
@@ -1652,7 +1652,7 @@
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
     </row>
-    <row r="95" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
       <c r="D95" s="2"/>
@@ -1662,7 +1662,7 @@
       <c r="H95" s="2"/>
       <c r="I95" s="2"/>
     </row>
-    <row r="96" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
@@ -1672,7 +1672,7 @@
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
     </row>
-    <row r="97" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
@@ -1682,7 +1682,7 @@
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
     </row>
-    <row r="98" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
       <c r="D98" s="2"/>
@@ -1692,7 +1692,7 @@
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
     </row>
-    <row r="99" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
@@ -1702,7 +1702,7 @@
       <c r="H99" s="2"/>
       <c r="I99" s="2"/>
     </row>
-    <row r="100" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
@@ -1712,7 +1712,7 @@
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
     </row>
-    <row r="101" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
@@ -1722,7 +1722,7 @@
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
     </row>
-    <row r="102" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
@@ -1732,7 +1732,7 @@
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
     </row>
-    <row r="103" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
@@ -1742,7 +1742,7 @@
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
     </row>
-    <row r="104" spans="2:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>

--- a/templates/xs_template.xlsx
+++ b/templates/xs_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36153880-F8FA-479E-8972-4A56E94D0260}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BF46C7-43A4-4B54-A1C7-409D8003786B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -141,7 +141,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
+      <sz val="25"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -358,29 +358,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -747,24 +747,24 @@
       </c>
     </row>
     <row r="6" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="10"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
     </row>
     <row r="7" spans="2:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="11"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="11"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="11"/>
-      <c r="I7" s="11"/>
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="17"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="17"/>
+      <c r="H7" s="17"/>
+      <c r="I7" s="17"/>
     </row>
     <row r="8" spans="2:9" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
@@ -794,403 +794,403 @@
     </row>
     <row r="9" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B9" s="7"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="13"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="10"/>
+      <c r="I9" s="11"/>
     </row>
     <row r="10" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B10" s="8"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="15"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+      <c r="I10" s="13"/>
     </row>
     <row r="11" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B11" s="8"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="15"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+      <c r="I11" s="13"/>
     </row>
     <row r="12" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B12" s="8"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="15"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+      <c r="I12" s="13"/>
     </row>
     <row r="13" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B13" s="8"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="13"/>
     </row>
     <row r="14" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B14" s="8"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="13"/>
     </row>
     <row r="15" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B15" s="8"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="13"/>
     </row>
     <row r="16" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B16" s="8"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="13"/>
     </row>
     <row r="17" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B17" s="8"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="13"/>
     </row>
     <row r="18" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B18" s="8"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="13"/>
     </row>
     <row r="19" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B19" s="8"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="13"/>
     </row>
     <row r="20" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B20" s="8"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="13"/>
     </row>
     <row r="21" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B21" s="8"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="13"/>
     </row>
     <row r="22" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B22" s="8"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="13"/>
     </row>
     <row r="23" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B23" s="8"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="13"/>
     </row>
     <row r="24" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B24" s="8"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="13"/>
     </row>
     <row r="25" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B25" s="8"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="13"/>
     </row>
     <row r="26" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B26" s="8"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="13"/>
     </row>
     <row r="27" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B27" s="8"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="13"/>
     </row>
     <row r="28" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B28" s="8"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="13"/>
     </row>
     <row r="29" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B29" s="8"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="13"/>
     </row>
     <row r="30" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B30" s="8"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="13"/>
     </row>
     <row r="31" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B31" s="8"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="13"/>
     </row>
     <row r="32" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B32" s="8"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="13"/>
     </row>
     <row r="33" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B33" s="8"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="13"/>
     </row>
     <row r="34" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B34" s="8"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="13"/>
     </row>
     <row r="35" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B35" s="8"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="13"/>
     </row>
     <row r="36" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B36" s="8"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="13"/>
     </row>
     <row r="37" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B37" s="8"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15"/>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="13"/>
     </row>
     <row r="38" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B38" s="8"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15"/>
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12"/>
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="13"/>
     </row>
     <row r="39" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B39" s="8"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15"/>
+      <c r="C39" s="12"/>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
+      <c r="F39" s="12"/>
+      <c r="G39" s="12"/>
+      <c r="H39" s="12"/>
+      <c r="I39" s="13"/>
     </row>
     <row r="40" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B40" s="8"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="14"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15"/>
+      <c r="C40" s="12"/>
+      <c r="D40" s="12"/>
+      <c r="E40" s="12"/>
+      <c r="F40" s="12"/>
+      <c r="G40" s="12"/>
+      <c r="H40" s="12"/>
+      <c r="I40" s="13"/>
     </row>
     <row r="41" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B41" s="8"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="12"/>
+      <c r="G41" s="12"/>
+      <c r="H41" s="12"/>
+      <c r="I41" s="13"/>
     </row>
     <row r="42" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B42" s="8"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="12"/>
+      <c r="G42" s="12"/>
+      <c r="H42" s="12"/>
+      <c r="I42" s="13"/>
     </row>
     <row r="43" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B43" s="8"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="13"/>
     </row>
     <row r="44" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B44" s="8"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15"/>
+      <c r="C44" s="12"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="12"/>
+      <c r="G44" s="12"/>
+      <c r="H44" s="12"/>
+      <c r="I44" s="13"/>
     </row>
     <row r="45" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B45" s="8"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15"/>
+      <c r="C45" s="12"/>
+      <c r="D45" s="12"/>
+      <c r="E45" s="12"/>
+      <c r="F45" s="12"/>
+      <c r="G45" s="12"/>
+      <c r="H45" s="12"/>
+      <c r="I45" s="13"/>
     </row>
     <row r="46" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B46" s="8"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15"/>
+      <c r="C46" s="12"/>
+      <c r="D46" s="12"/>
+      <c r="E46" s="12"/>
+      <c r="F46" s="12"/>
+      <c r="G46" s="12"/>
+      <c r="H46" s="12"/>
+      <c r="I46" s="13"/>
     </row>
     <row r="47" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B47" s="8"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15"/>
+      <c r="C47" s="12"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="12"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="12"/>
+      <c r="I47" s="13"/>
     </row>
     <row r="48" spans="2:9" ht="15" x14ac:dyDescent="0.25">
       <c r="B48" s="9"/>
-      <c r="C48" s="16"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="16"/>
-      <c r="G48" s="16"/>
-      <c r="H48" s="16"/>
-      <c r="I48" s="17"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+      <c r="G48" s="14"/>
+      <c r="H48" s="14"/>
+      <c r="I48" s="15"/>
     </row>
     <row r="49" spans="2:9" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B49" s="2"/>

--- a/templates/xs_template.xlsx
+++ b/templates/xs_template.xlsx
@@ -8,17 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BF46C7-43A4-4B54-A1C7-409D8003786B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF490C0-8283-4188-87F8-CA5D102E86E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -141,7 +150,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="25"/>
+      <sz val="18"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -451,6 +460,50 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>18419</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF139D4B-69D6-4CF0-9B88-E66AAE6CB969}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10795000" y="241300"/>
+          <a:ext cx="1028069" cy="1295400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/templates/xs_template.xlsx
+++ b/templates/xs_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF490C0-8283-4188-87F8-CA5D102E86E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{462811E6-2D08-4E70-B0F1-6C29AF3CD75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -395,7 +395,29 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color rgb="FF00B050"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2982,5 +3004,36 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="65" orientation="landscape" r:id="rId1"/>
   <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="containsText" priority="2" operator="containsText" id="{1C273855-0DFC-4DED-8EB7-87955D5053D8}">
+            <xm:f>NOT(ISERROR(SEARCH("SIM",C9)))</xm:f>
+            <xm:f>"SIM"</xm:f>
+            <x14:dxf>
+              <font>
+                <b/>
+                <i val="0"/>
+                <color rgb="FF00B050"/>
+              </font>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="containsText" priority="1" operator="containsText" id="{D1788155-BA8F-42EC-81DF-1B41BB3108EC}">
+            <xm:f>NOT(ISERROR(SEARCH("NÃO",C9)))</xm:f>
+            <xm:f>"NÃO"</xm:f>
+            <x14:dxf>
+              <font>
+                <b/>
+                <i val="0"/>
+                <color rgb="FFFF0000"/>
+              </font>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>C9:C48</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
 </worksheet>
 </file>